--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Level</t>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Type d'établissement</t>
+  </si>
+  <si>
+    <t>secteurActiviteRASS</t>
+  </si>
+  <si>
+    <t>Secteur d'activité RASS</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -538,6 +544,20 @@
         <v>48</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/110-creation-exemples/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
